--- a/ABUSvsUS_lab.xlsx
+++ b/ABUSvsUS_lab.xlsx
@@ -1542,7 +1542,7 @@
         <v>46</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
@@ -1998,7 +1998,7 @@
         <v>46</v>
       </c>
       <c r="J37" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
@@ -2112,7 +2112,7 @@
         <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
@@ -2530,7 +2530,7 @@
         <v>17</v>
       </c>
       <c r="J51" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
@@ -6824,7 +6824,7 @@
         <v>17</v>
       </c>
       <c r="J164" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K164" t="s">
         <v>15</v>
@@ -9864,7 +9864,7 @@
         <v>46</v>
       </c>
       <c r="J244" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K244" t="s">
         <v>15</v>
@@ -11080,7 +11080,7 @@
         <v>46</v>
       </c>
       <c r="J276" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K276" t="s">
         <v>15</v>
@@ -12220,7 +12220,7 @@
         <v>46</v>
       </c>
       <c r="J306" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K306" t="s">
         <v>15</v>
@@ -16856,7 +16856,7 @@
         <v>17</v>
       </c>
       <c r="J428" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K428" t="s">
         <v>15</v>
@@ -18300,7 +18300,7 @@
         <v>17</v>
       </c>
       <c r="J466" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K466" t="s">
         <v>15</v>
@@ -19022,7 +19022,7 @@
         <v>46</v>
       </c>
       <c r="J485" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K485" t="s">
         <v>15</v>
@@ -20884,7 +20884,7 @@
         <v>46</v>
       </c>
       <c r="J534" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K534" t="s">
         <v>15</v>
@@ -21682,7 +21682,7 @@
         <v>17</v>
       </c>
       <c r="J555" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K555" t="s">
         <v>15</v>
@@ -26850,7 +26850,7 @@
         <v>17</v>
       </c>
       <c r="J691" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K691" t="s">
         <v>15</v>
@@ -28940,7 +28940,7 @@
         <v>25</v>
       </c>
       <c r="J746" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K746" t="s">
         <v>15</v>
@@ -29434,7 +29434,7 @@
         <v>17</v>
       </c>
       <c r="J759" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K759" t="s">
         <v>15</v>
@@ -30422,7 +30422,7 @@
         <v>17</v>
       </c>
       <c r="J785" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K785" t="s">
         <v>15</v>
@@ -30460,7 +30460,7 @@
         <v>17</v>
       </c>
       <c r="J786" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K786" t="s">
         <v>15</v>
@@ -31524,7 +31524,7 @@
         <v>25</v>
       </c>
       <c r="J814" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K814" t="s">
         <v>15</v>
@@ -33272,7 +33272,7 @@
         <v>17</v>
       </c>
       <c r="J860" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K860" t="s">
         <v>15</v>
@@ -37528,7 +37528,7 @@
         <v>25</v>
       </c>
       <c r="J972" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K972" t="s">
         <v>15</v>
@@ -37566,7 +37566,7 @@
         <v>25</v>
       </c>
       <c r="J973" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K973" t="s">
         <v>15</v>
@@ -38288,7 +38288,7 @@
         <v>25</v>
       </c>
       <c r="J992" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K992" t="s">
         <v>15</v>
@@ -38858,7 +38858,7 @@
         <v>25</v>
       </c>
       <c r="J1007" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1007" t="s">
         <v>15</v>
@@ -40264,7 +40264,7 @@
         <v>25</v>
       </c>
       <c r="J1044" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1044" t="s">
         <v>15</v>
@@ -41442,7 +41442,7 @@
         <v>25</v>
       </c>
       <c r="J1075" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1075" t="s">
         <v>15</v>
@@ -44558,7 +44558,7 @@
         <v>25</v>
       </c>
       <c r="J1157" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1157" t="s">
         <v>15</v>
@@ -45166,7 +45166,7 @@
         <v>25</v>
       </c>
       <c r="J1173" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1173" t="s">
         <v>15</v>
@@ -50942,7 +50942,7 @@
         <v>25</v>
       </c>
       <c r="J1325" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K1325" t="s">
         <v>15</v>
